--- a/data/trans_dic/P40_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P40_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,59; 21,34</t>
+          <t>12,12; 21,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 27,24</t>
+          <t>17,61; 27,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,26; 30,42</t>
+          <t>19,75; 30,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,32; 30,36</t>
+          <t>19,86; 29,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,94; 26,27</t>
+          <t>16,04; 26,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,19; 46,44</t>
+          <t>33,86; 45,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,68; 40,45</t>
+          <t>28,1; 39,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,95; 38,8</t>
+          <t>29,04; 37,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,82</t>
+          <t>15,05; 21,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,9; 34,86</t>
+          <t>26,86; 34,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,74; 33,25</t>
+          <t>25,74; 33,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,36; 33,25</t>
+          <t>26,02; 32,14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 18,84</t>
+          <t>11,89; 18,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 19,92</t>
+          <t>12,64; 19,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 14,96</t>
+          <t>9,08; 15,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 20,51</t>
+          <t>12,51; 20,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 32,54</t>
+          <t>24,68; 32,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 34,43</t>
+          <t>26,35; 33,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 26,93</t>
+          <t>19,02; 27,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,43</t>
+          <t>18,95; 25,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,48; 24,63</t>
+          <t>19,46; 24,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,55; 25,99</t>
+          <t>20,62; 26,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 19,89</t>
+          <t>14,74; 19,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 21,54</t>
+          <t>16,84; 21,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 20,88</t>
+          <t>11,84; 19,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 22,8</t>
+          <t>13,67; 22,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,04; 21,04</t>
+          <t>12,85; 20,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,08</t>
+          <t>19,45; 27,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,01</t>
+          <t>25,42; 35,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 30,94</t>
+          <t>20,99; 30,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 26,05</t>
+          <t>16,23; 25,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 32,75</t>
+          <t>25,1; 32,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,23</t>
+          <t>19,91; 26,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,64; 25,21</t>
+          <t>18,97; 25,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 21,86</t>
+          <t>15,97; 22,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,31; 29,26</t>
+          <t>23,29; 28,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,78</t>
+          <t>9,67; 16,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,05; 23,17</t>
+          <t>14,51; 23,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 22,91</t>
+          <t>13,85; 22,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 27,05</t>
+          <t>15,47; 25,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 31,4</t>
+          <t>22,4; 31,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,45; 38,58</t>
+          <t>29,1; 38,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,86; 37,64</t>
+          <t>27,26; 37,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 62,0</t>
+          <t>25,03; 33,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 23,01</t>
+          <t>16,97; 22,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 29,64</t>
+          <t>22,98; 29,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 28,89</t>
+          <t>22,4; 28,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,66; 49,7</t>
+          <t>21,78; 28,35</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 31,55</t>
+          <t>19,2; 31,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 23,84</t>
+          <t>13,15; 24,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 21,32</t>
+          <t>11,05; 20,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,81</t>
+          <t>9,48; 16,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,21; 45,81</t>
+          <t>32,17; 45,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,07; 37,91</t>
+          <t>25,67; 37,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,62; 34,08</t>
+          <t>21,47; 33,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,34; 26,78</t>
+          <t>18,42; 25,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,39</t>
+          <t>27,27; 36,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 29,46</t>
+          <t>21,32; 29,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 25,91</t>
+          <t>17,85; 25,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,06; 21,54</t>
+          <t>15,1; 20,07</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,28</t>
+          <t>10,72; 18,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 24,24</t>
+          <t>14,04; 23,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,42</t>
+          <t>15,12; 24,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,91; 27,15</t>
+          <t>18,46; 26,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 41,21</t>
+          <t>29,57; 40,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 32,68</t>
+          <t>21,59; 32,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,3; 34,12</t>
+          <t>23,34; 34,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,47; 38,08</t>
+          <t>29,11; 38,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,57; 28,71</t>
+          <t>21,44; 28,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 26,23</t>
+          <t>19,13; 26,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,76</t>
+          <t>20,61; 28,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,98; 31,13</t>
+          <t>25,01; 30,86</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,6; 17,14</t>
+          <t>11,39; 17,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,96</t>
+          <t>12,91; 19,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,65</t>
+          <t>12,71; 18,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,52; 19,63</t>
+          <t>13,31; 19,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,96</t>
+          <t>24,9; 32,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,2; 27,84</t>
+          <t>21,43; 27,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,87; 29,86</t>
+          <t>22,59; 29,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 27,32</t>
+          <t>23,83; 29,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 23,57</t>
+          <t>19,15; 23,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,15; 22,82</t>
+          <t>18,06; 22,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,67; 23,21</t>
+          <t>18,71; 23,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 22,27</t>
+          <t>19,51; 23,68</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,77; 20,28</t>
+          <t>15,0; 20,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,13; 17,38</t>
+          <t>12,09; 17,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,77</t>
+          <t>11,01; 16,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 19,82</t>
+          <t>16,11; 21,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,32; 29,69</t>
+          <t>23,17; 29,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,07; 21,59</t>
+          <t>16,05; 21,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,44; 22,37</t>
+          <t>16,31; 22,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,31; 31,84</t>
+          <t>25,83; 30,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,79; 24,17</t>
+          <t>20,0; 24,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 18,64</t>
+          <t>14,94; 18,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 18,45</t>
+          <t>14,63; 18,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 24,79</t>
+          <t>21,61; 25,24</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,71; 17,33</t>
+          <t>14,75; 17,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,39</t>
+          <t>15,55; 18,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,75; 17,31</t>
+          <t>14,71; 17,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,84</t>
+          <t>17,4; 20,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,93; 30,15</t>
+          <t>27,01; 30,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,36; 28,47</t>
+          <t>25,47; 28,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,67; 26,78</t>
+          <t>23,74; 26,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,89; 31,29</t>
+          <t>26,29; 28,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,37</t>
+          <t>21,3; 23,41</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,04</t>
+          <t>20,89; 23,09</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,59</t>
+          <t>19,68; 21,74</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,98; 25,17</t>
+          <t>22,35; 24,11</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77700</t>
+          <t>79340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96927</t>
+          <t>104051</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>174628</t>
+          <t>183391</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34371; 58271</t>
+          <t>33095; 58140</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51032; 79192</t>
+          <t>51205; 79384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58824; 88315</t>
+          <t>57348; 87365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63282; 94548</t>
+          <t>63317; 93825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41572; 68517</t>
+          <t>41826; 69322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94312; 131971</t>
+          <t>96230; 129820</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82791; 116793</t>
+          <t>81127; 114757</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83845; 112387</t>
+          <t>91791; 118054</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81960; 116480</t>
+          <t>80362; 116861</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154636; 200429</t>
+          <t>154440; 198816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149062; 192529</t>
+          <t>149011; 194151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>152444; 199832</t>
+          <t>165221; 204080</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83391</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>113914</t>
+          <t>120686</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>197305</t>
+          <t>205673</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60888; 92899</t>
+          <t>58639; 91145</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64452; 99910</t>
+          <t>63394; 98271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45552; 75024</t>
+          <t>45523; 76064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66379; 106307</t>
+          <t>66388; 106472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125512; 163993</t>
+          <t>124374; 164624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>136664; 179962</t>
+          <t>137734; 176861</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>101053; 140299</t>
+          <t>99095; 142232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>99539; 130943</t>
+          <t>103577; 136910</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194254; 245612</t>
+          <t>194019; 247181</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210483; 266289</t>
+          <t>211283; 267745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152357; 203368</t>
+          <t>150684; 202006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>171653; 222551</t>
+          <t>181411; 230893</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73544</t>
+          <t>73283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100610</t>
+          <t>102746</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>174155</t>
+          <t>176029</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39576; 66585</t>
+          <t>37736; 63303</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44565; 73459</t>
+          <t>44047; 72686</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41047; 66246</t>
+          <t>40458; 64651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61342; 88756</t>
+          <t>61453; 87988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85271; 117443</t>
+          <t>85278; 117545</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72477; 105512</t>
+          <t>71564; 104888</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54723; 86404</t>
+          <t>53828; 83752</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87809; 114332</t>
+          <t>89440; 117080</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132103; 171630</t>
+          <t>130284; 172420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123594; 167174</t>
+          <t>125781; 169174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102671; 141334</t>
+          <t>103289; 142452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>155028; 194643</t>
+          <t>156614; 194526</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67993</t>
+          <t>73982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>121828</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>248633</t>
+          <t>195810</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34931; 60000</t>
+          <t>34574; 59778</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55410; 85280</t>
+          <t>53405; 84708</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54616; 84352</t>
+          <t>50983; 84011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52882; 84536</t>
+          <t>57723; 93918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85145; 116651</t>
+          <t>83217; 117984</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114266; 149713</t>
+          <t>112910; 149511</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107364; 145052</t>
+          <t>105043; 144170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>121018; 294949</t>
+          <t>105631; 140648</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125369; 167790</t>
+          <t>123755; 167170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>174850; 224085</t>
+          <t>173749; 222204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>165285; 217677</t>
+          <t>168763; 218227</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>186515; 391752</t>
+          <t>173210; 225384</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72221</t>
+          <t>75639</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39321; 63872</t>
+          <t>38868; 64621</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27887; 50450</t>
+          <t>27821; 51430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24105; 44027</t>
+          <t>22809; 42515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18199; 31836</t>
+          <t>19506; 34850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66900; 95133</t>
+          <t>66810; 94352</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54834; 82918</t>
+          <t>56139; 82946</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46691; 73625</t>
+          <t>46386; 72687</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40286; 55784</t>
+          <t>41791; 57189</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112547; 149220</t>
+          <t>111823; 151660</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91229; 126743</t>
+          <t>91736; 127469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76777; 109479</t>
+          <t>75404; 109410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62152; 83355</t>
+          <t>65318; 86800</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60972</t>
+          <t>59985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>88150</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>147283</t>
+          <t>148135</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28795; 52209</t>
+          <t>29032; 51144</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38304; 65922</t>
+          <t>38168; 64709</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40987; 66631</t>
+          <t>39646; 64956</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50998; 73200</t>
+          <t>49978; 71252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83272; 114624</t>
+          <t>82236; 113549</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62131; 91159</t>
+          <t>60217; 90206</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63642; 93178</t>
+          <t>63746; 93606</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75761; 97893</t>
+          <t>76779; 100543</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118433; 157616</t>
+          <t>117712; 157297</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105951; 144495</t>
+          <t>105380; 146114</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110633; 148597</t>
+          <t>110314; 152737</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131581; 163938</t>
+          <t>133673; 164931</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>114971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>169461</t>
+          <t>206399</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>271080</t>
+          <t>321369</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>71241; 105262</t>
+          <t>69929; 105758</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84129; 123658</t>
+          <t>84162; 124131</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84480; 121799</t>
+          <t>83006; 123538</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84420; 122567</t>
+          <t>95819; 137905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>158000; 203430</t>
+          <t>158479; 204810</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>146275; 192089</t>
+          <t>147881; 193106</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>156098; 203849</t>
+          <t>154176; 202280</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>79475; 231981</t>
+          <t>183966; 229304</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>238914; 294725</t>
+          <t>239428; 294445</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>243610; 306218</t>
+          <t>242454; 307092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>249423; 309998</t>
+          <t>249953; 310130</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>177755; 328155</t>
+          <t>291037; 353297</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129727</t>
+          <t>145487</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>235604</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>337602</t>
+          <t>381091</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>109861; 150809</t>
+          <t>111537; 154880</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>92668; 132791</t>
+          <t>92387; 134073</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86222; 122466</t>
+          <t>85520; 125162</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61130; 184064</t>
+          <t>128534; 168493</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>182723; 232643</t>
+          <t>181524; 231993</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>130368; 175211</t>
+          <t>130260; 175760</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>134127; 182449</t>
+          <t>133026; 180939</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>188870; 228559</t>
+          <t>214759; 257418</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>302200; 369089</t>
+          <t>305449; 372976</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>233538; 293688</t>
+          <t>235306; 296121</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>232743; 293859</t>
+          <t>232942; 293025</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>204155; 408220</t>
+          <t>352099; 411315</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>619265</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1003641</t>
+          <t>1028610</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1622905</t>
+          <t>1687138</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>481701; 567352</t>
+          <t>483004; 563588</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>528047; 622007</t>
+          <t>526094; 622642</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>497444; 583985</t>
+          <t>496042; 586909</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>486494; 686297</t>
+          <t>614602; 707202</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>909699; 1018360</t>
+          <t>912314; 1019541</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>896634; 1006458</t>
+          <t>900356; 1007094</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>831911; 941096</t>
+          <t>834271; 941753</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>838084; 1145921</t>
+          <t>981802; 1075953</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1423286; 1554451</t>
+          <t>1416684; 1557011</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1455899; 1594040</t>
+          <t>1445032; 1597084</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1361681; 1486878</t>
+          <t>1355349; 1497447</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1422663; 1792229</t>
+          <t>1624541; 1752315</t>
         </is>
       </c>
     </row>
